--- a/pseudodata/1001.xlsx
+++ b/pseudodata/1001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,28 +536,28 @@
         <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.003079333255803665</v>
+        <v>-0.0006411002443443207</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001678728422073025</v>
+        <v>0.001142940873402372</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0001539666627901833</v>
+        <v>-3.205501221721604e-05</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -590,28 +590,28 @@
         <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.003006949307339891</v>
+        <v>-0.0008634859872505839</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002262896937844999</v>
+        <v>0.001164001788010422</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0001503474653669945</v>
+        <v>-4.317429936252919e-05</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -644,28 +644,28 @@
         <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.002043946354555173</v>
+        <v>-0.001123042542067654</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003189842686342667</v>
+        <v>0.001273352133360757</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0001021973177277587</v>
+        <v>-5.615212710338271e-05</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -698,28 +698,28 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0004607113480824245</v>
+        <v>-0.001461251073788138</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0004546963916241558</v>
+        <v>0.00148176781154267</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.303556740412122e-05</v>
+        <v>-7.306255368940689e-05</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -752,28 +752,28 @@
         <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001543065669891697</v>
+        <v>-0.001930657635087965</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0006477184813343971</v>
+        <v>0.00181391800676652</v>
       </c>
       <c r="N6" t="n">
-        <v>7.715328349458487e-05</v>
+        <v>-9.653288175439826e-05</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -806,28 +806,28 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003810855295206269</v>
+        <v>-0.002591332123535291</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0008982317354201029</v>
+        <v>0.002306872471346448</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001905427647603135</v>
+        <v>-0.0001295666061767646</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -860,28 +860,28 @@
         <v>0.1</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006005226104739806</v>
+        <v>-0.00350612702292311</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00118439124119005</v>
+        <v>0.003009241073292013</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0003002613052369903</v>
+        <v>-0.0001753063511461555</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -908,34 +908,34 @@
         <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
         <v>0.1</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0009429285995471301</v>
+        <v>-0.004738003889388833</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001678728422073025</v>
+        <v>0.003981718005276101</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.714642997735651e-05</v>
+        <v>-0.0002369001944694416</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -962,34 +962,34 @@
         <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.001444926920518763</v>
+        <v>-0.006355961735605872</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0002262896937844999</v>
+        <v>0.00529886988664022</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.224634602593813e-05</v>
+        <v>-0.0003177980867802937</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1016,34 +1016,34 @@
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
         <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.00151732373802449</v>
+        <v>-0.008447143432763825</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0003189842686342667</v>
+        <v>0.007042667993800811</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.586618690122449e-05</v>
+        <v>-0.0004223571716381913</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1070,34 +1070,34 @@
         <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
         <v>0.1</v>
       </c>
       <c r="I12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.001170100082762613</v>
+        <v>-0.01110350173622898</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0004546963916241558</v>
+        <v>0.009267656773983002</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.850500413813066e-05</v>
+        <v>-0.0005551750868114489</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1124,34 +1124,34 @@
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
         <v>0.1</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0005277022661412283</v>
+        <v>-0.0143311444809686</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0006477184813343971</v>
+        <v>0.01194042617707822</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.638511330706142e-05</v>
+        <v>-0.00071655722404843</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1178,34 +1178,34 @@
         <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0002729010600625739</v>
+        <v>-0.0179414341322815</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0008982317354201029</v>
+        <v>0.01494261161490651</v>
       </c>
       <c r="N14" t="n">
-        <v>1.364505300312869e-05</v>
+        <v>-0.0008970717066140752</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1232,34 +1232,34 @@
         <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
       </c>
       <c r="I15" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001186628626672392</v>
+        <v>-0.02168739987944248</v>
       </c>
       <c r="M15" t="n">
-        <v>0.00118439124119005</v>
+        <v>0.01823655223636005</v>
       </c>
       <c r="N15" t="n">
-        <v>5.933143133361962e-05</v>
+        <v>-0.001084369993972124</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1286,34 +1286,34 @@
         <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0002004394139297718</v>
+        <v>-0.02561778505888466</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0001678728422073025</v>
+        <v>0.02202774076246491</v>
       </c>
       <c r="N16" t="n">
-        <v>1.002197069648859e-05</v>
+        <v>-0.001280889252944233</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1340,34 +1340,34 @@
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="H17" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>2.507216030101972e-05</v>
+        <v>-0.03014863330692746</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0002262896937844999</v>
+        <v>0.02664922837301635</v>
       </c>
       <c r="N17" t="n">
-        <v>1.253608015050986e-06</v>
+        <v>-0.001507431665346373</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1394,253 +1394,37 @@
         <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
         <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0001813747341237582</v>
+        <v>-0.03567178363475463</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0003189842686342667</v>
+        <v>0.03219062720740762</v>
       </c>
       <c r="N18" t="n">
-        <v>-9.068736706187911e-06</v>
+        <v>-0.001783589181737732</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>50</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>100</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-0.000403235870869655</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.0004546963916241558</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-2.016179354348275e-05</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>100</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>50</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>100</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-0.0006223160283425346</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.0006477184813343971</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-3.111580141712674e-05</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>100</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>50</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>100</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-0.0008130809721881393</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.0008982317354201029</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-4.065404860940697e-05</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>50</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>100</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-0.0009247133903544681</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.00118439124119005</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-4.623566951772341e-05</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
         <v>1</v>
       </c>
     </row>
